--- a/04_DESIGN_TABLES/DesignTable_6502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6502.xlsx
@@ -550,12 +550,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=0.6~0.600; M6@DRIVE=0.94~0.940; M2@DRIVE=0.72~0.720; Y@HEX=0.44~0.438; C3HEX@HEX=0.56~0.563; D1@BORE=0.17~0.172; D2@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -678,12 +683,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=0.63~0.630; M6@DRIVE=1~1.000; M2@DRIVE=0.77~0.770; Y@HEX=0.56~0.562; C3HEX@HEX=0.63~0.625; D1@BORE=0.23~0.234; D2@BORE=0.23~0.234</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -806,12 +816,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=0.75~0.750; M6@DRIVE=1.12~1.120; M2@DRIVE=0.83~0.830; Y@HEX=0.56~0.562; C3HEX@HEX=0.69~0.688; D1@BORE=0.3~0.297; D2@BORE=0.3~0.297</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -963,7 +978,7 @@
         <v>0.98</v>
       </c>
       <c r="C10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="D10" t="n">
         <v>0.86</v>
@@ -1003,7 +1018,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows)</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M6@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1963 = 1.280 (table had 1.25) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M6@DRIVE 1.25 -&gt; OMi 1.280 (Items!O1963, M135)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1126,12 +1146,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=0.94~0.940; M6@DRIVE=1.44~1.440; M2@DRIVE=1.11~1.110; Y@HEX=0.88~0.875; C3HEX@HEX=1~1.000; D1@BORE=0.48~0.484; D2@BORE=0.48~0.484</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1222,7 +1247,7 @@
         <v>1.5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E14" t="n">
         <v>1.25</v>
@@ -1259,7 +1284,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows)</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1967 = 0.930 (table had 0.94) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 0.94 -&gt; OMi 0.930 (Items!N1967, M134)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1446,7 +1476,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1456,12 +1486,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p035-t02: agrees on M2@DRIVE, M6@DRIVE, C3HEX@HEX, Y@HEX, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>6502-16-16-FG</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1577,7 @@
         <v>2.03</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -1579,7 +1614,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows)</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1972 = 1.410 (table had 1.4) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 1.4 -&gt; OMi 1.410 (Items!N1972, M134)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1702,12 +1742,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=1.52~1.520; M6@DRIVE=2.25~2.250; M2@DRIVE=1.78~1.780; Y@HEX=1.88~1.875; C3HEX@HEX=2.25~2.250; D1@BORE=1.31~1.312; D2@BORE=1.31~1.312</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1824,12 +1869,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=1.97~1.970; M6@DRIVE=2.91~2.910; M2@DRIVE=2.22~2.220; Y@HEX=2.5~2.500; C3HEX@HEX=2.88~2.875; D1@BORE=1.78~1.781; D2@BORE=1.78~1.781</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6502.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -978,7 +978,7 @@
         <v>0.98</v>
       </c>
       <c r="C10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="D10" t="n">
         <v>0.86</v>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows); M6@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1963 = 1.280 (table had 1.25) [user 2026-10-18 A19]</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M6@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1963 = 1.280 (table had 1.25) [user 2026-10-18 A19]; M6@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M6@DRIVE 1.25 -&gt; OMi 1.280 (Items!O1963, M135)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M6@DRIVE 1.25 -&gt; OMi 1.280 (Items!O1963, M135) | 2026-10-20 Air-Way first: M6@DRIVE OMi/Brennan 1.28 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1247,7 +1247,7 @@
         <v>1.5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>1.25</v>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1967 = 0.930 (table had 0.94) [user 2026-10-18 A19]</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1967 = 0.930 (table had 0.94) [user 2026-10-18 A19]; M14@DRIVE: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.93) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 0.94 -&gt; OMi 0.930 (Items!N1967, M134)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 0.94 -&gt; OMi 0.930 (Items!N1967, M134) | 2026-10-20 Air-Way first: M14@DRIVE OMi/Brennan 0.93 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1577,7 +1577,7 @@
         <v>2.03</v>
       </c>
       <c r="D19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1972 = 1.410 (table had 1.4) [user 2026-10-18 A19]</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1972 = 1.410 (table had 1.4) [user 2026-10-18 A19]; M14@DRIVE: Air-Way 1.4 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 1.4 -&gt; OMi 1.410 (Items!N1972, M134)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 1.4 -&gt; OMi 1.410 (Items!N1972, M134) | 2026-10-20 Air-Way first: M14@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6502.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2143,24 +2143,56 @@
           <t>6502-16-12-FG</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>6502-16-12-FG</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B (1) UN/UNF-2A) x 1 1/16-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | 2026-10-20 (batch 19 D_geom): every size from OMi WebsitePartsInfo2026.xlsx (07_RAW_EXTRACTS/omi_dimensions, sha256 e5109342e141...) Items row 1969 (M2 1.47, M6 1.70, M14 1.14, nut hex 1.25, flats 1.312, D1 0.844, D2 0.609; = the Brennan TFA catalog p.35 6502-16-12-FG row on all 7 values, one source) - ASSUMED; thread majors from the JIC end library (batch-15 precedent: 6502-10-08-FG)</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20: filled from OMi's file row 1969 (= Brennan TFA p.35), ASSUMED; Air-Way prints no 6502-16-12 row</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
